--- a/VerveStacks_COL/vt_vervestacks_COL_v1.xlsx
+++ b/VerveStacks_COL/vt_vervestacks_COL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_COL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8D1A307-FB53-4999-8F8D-C99FA9B849AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDDE3AD8-2E27-49C6-BEC8-89D6B4D53624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1CDAB499-A377-4BA9-9611-96FF44454A21}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{26F366DD-5BD1-406A-BA87-099DCFDB199B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2059,7 +2059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA9D9C2-CC9E-4BD3-B560-DAB71275F7B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99FADAE-7F9C-432B-8713-27078C84E94C}">
   <dimension ref="B9:T47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2138,7 +2138,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.10069392000000002</v>
+        <v>7.0485744000000017E-2</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -2194,19 +2194,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.132192</v>
+        <v>6.9457920000000006E-2</v>
       </c>
       <c r="F12">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G12">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I12">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -2250,19 +2250,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.132192</v>
+        <v>6.9457920000000006E-2</v>
       </c>
       <c r="F13">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G13">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I13">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -2306,19 +2306,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.128304</v>
+        <v>6.7415040000000023E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>20</v>
@@ -2362,19 +2362,19 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.128304</v>
+        <v>6.7415040000000023E-2</v>
       </c>
       <c r="F15">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G15">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H15">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I15">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J15" t="s">
         <v>21</v>
@@ -2418,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>8.4633600000000017E-2</v>
+        <v>5.9243520000000001E-2</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -2474,7 +2474,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>9.3388800000000008E-2</v>
+        <v>6.5372160000000012E-2</v>
       </c>
       <c r="F17">
         <v>3583</v>
@@ -2530,19 +2530,19 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.128304</v>
+        <v>6.7415040000000023E-2</v>
       </c>
       <c r="F18">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G18">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H18">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I18">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J18" t="s">
         <v>24</v>
@@ -2586,19 +2586,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.132192</v>
+        <v>6.9457920000000006E-2</v>
       </c>
       <c r="F19">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G19">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H19">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I19">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J19" t="s">
         <v>25</v>
@@ -2642,19 +2642,19 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.128304</v>
+        <v>6.7415040000000023E-2</v>
       </c>
       <c r="F20">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G20">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H20">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I20">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2698,19 +2698,19 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.132192</v>
+        <v>6.9457920000000006E-2</v>
       </c>
       <c r="F21">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G21">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H21">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I21">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J21" t="s">
         <v>27</v>
@@ -2754,7 +2754,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>8.4633600000000017E-2</v>
+        <v>5.9243520000000001E-2</v>
       </c>
       <c r="F22">
         <v>3583</v>
@@ -2810,7 +2810,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>9.3388800000000008E-2</v>
+        <v>6.5372160000000012E-2</v>
       </c>
       <c r="F23">
         <v>3583</v>
@@ -2866,19 +2866,19 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.128304</v>
+        <v>6.7415040000000023E-2</v>
       </c>
       <c r="F24">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G24">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H24">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I24">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J24" t="s">
         <v>30</v>
@@ -2922,19 +2922,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.132192</v>
+        <v>6.9457920000000006E-2</v>
       </c>
       <c r="F25">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G25">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H25">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I25">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J25" t="s">
         <v>31</v>
@@ -2978,7 +2978,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.42</v>
+        <v>0.29399999999999993</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3034,7 +3034,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.45779999999999998</v>
+        <v>0.32045999999999997</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3090,7 +3090,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.41999999999999993</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3146,7 +3146,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.42</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3202,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.504</v>
+        <v>0.35279999999999995</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3258,7 +3258,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.441</v>
+        <v>0.30870000000000003</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -3314,7 +3314,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.48719999999999997</v>
+        <v>0.3410399999999999</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -3370,7 +3370,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.42</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -3426,7 +3426,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.21420000000000003</v>
+        <v>0.14993999999999999</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -3482,7 +3482,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.22260000000000002</v>
+        <v>0.15581999999999999</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -3538,7 +3538,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.21420000000000003</v>
+        <v>0.14993999999999999</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -3594,7 +3594,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.21420000000000003</v>
+        <v>0.14993999999999999</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -3650,7 +3650,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.252</v>
+        <v>0.17639999999999997</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -3706,7 +3706,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.252</v>
+        <v>0.17639999999999997</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -3762,7 +3762,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3818,7 +3818,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.29820000000000002</v>
+        <v>0.20873999999999998</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3874,7 +3874,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.3024</v>
+        <v>0.21167999999999998</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -3930,7 +3930,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -3986,7 +3986,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4042,7 +4042,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4098,7 +4098,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4154,7 +4154,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.26039999999999996</v>
+        <v>0.18227999999999997</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4205,7 +4205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF2401E-EC15-47B5-8F3B-8391312AE1A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E228C2CC-FBAF-499F-B17C-0448BA84353F}">
   <dimension ref="B9:T163"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12163,7 +12163,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5953B6D1-8EDF-4DE6-9140-21DA2D0C881D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{747F3929-4405-4AF3-9A8B-153384E9437F}">
   <dimension ref="B9:T189"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12248,7 +12248,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G11">
-        <v>0.28799999999999998</v>
+        <v>0.20159999999999997</v>
       </c>
       <c r="H11">
         <v>4016.25</v>
@@ -12301,7 +12301,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G12">
-        <v>0.28799999999999998</v>
+        <v>0.20159999999999997</v>
       </c>
       <c r="H12">
         <v>4016.25</v>
@@ -12354,7 +12354,7 @@
         <v>0.27899999999999997</v>
       </c>
       <c r="G13">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H13">
         <v>3421.2499999999995</v>
@@ -12407,7 +12407,7 @@
         <v>4.0000000000000036E-3</v>
       </c>
       <c r="G14">
-        <v>0.33123000000000002</v>
+        <v>0.23186100000000001</v>
       </c>
       <c r="K14">
         <v>33</v>
@@ -12451,7 +12451,7 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="G15">
-        <v>0.32640000000000002</v>
+        <v>0.22847999999999999</v>
       </c>
       <c r="H15">
         <v>1955</v>
@@ -12504,7 +12504,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="G16">
-        <v>0.32640000000000002</v>
+        <v>0.22847999999999999</v>
       </c>
       <c r="H16">
         <v>1955</v>
@@ -12557,7 +12557,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G17">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H17">
         <v>1955</v>
@@ -12610,7 +12610,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G18">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H18">
         <v>1955</v>
@@ -12663,7 +12663,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G19">
-        <v>0.27839999999999998</v>
+        <v>0.19487999999999997</v>
       </c>
       <c r="H19">
         <v>2295</v>
@@ -12716,7 +12716,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G20">
-        <v>0.30719999999999997</v>
+        <v>0.21503999999999998</v>
       </c>
       <c r="H20">
         <v>1955</v>
@@ -12769,7 +12769,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G21">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H21">
         <v>1955</v>
@@ -12822,7 +12822,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="G22">
-        <v>0.32640000000000002</v>
+        <v>0.22847999999999999</v>
       </c>
       <c r="H22">
         <v>1955</v>
@@ -12875,7 +12875,7 @@
         <v>0.16300000000000001</v>
       </c>
       <c r="G23">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H23">
         <v>1955</v>
@@ -12928,7 +12928,7 @@
         <v>0.17</v>
       </c>
       <c r="G24">
-        <v>0.32640000000000002</v>
+        <v>0.22847999999999999</v>
       </c>
       <c r="H24">
         <v>1955</v>
@@ -12981,7 +12981,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G25">
-        <v>0.27839999999999998</v>
+        <v>0.19487999999999997</v>
       </c>
       <c r="H25">
         <v>2295</v>
@@ -13034,7 +13034,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G26">
-        <v>0.30719999999999997</v>
+        <v>0.21503999999999998</v>
       </c>
       <c r="H26">
         <v>1955</v>
@@ -13087,7 +13087,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G27">
-        <v>0.31680000000000003</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="H27">
         <v>1955</v>
@@ -13140,7 +13140,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G28">
-        <v>0.32640000000000002</v>
+        <v>0.22847999999999999</v>
       </c>
       <c r="H28">
         <v>1955</v>
@@ -13193,7 +13193,7 @@
         <v>0.24099999999999999</v>
       </c>
       <c r="G29">
-        <v>0.48</v>
+        <v>0.33599999999999991</v>
       </c>
       <c r="H29">
         <v>977.5</v>
@@ -13246,7 +13246,7 @@
         <v>0.46</v>
       </c>
       <c r="G30">
-        <v>0.5232</v>
+        <v>0.36623999999999995</v>
       </c>
       <c r="H30">
         <v>850</v>
@@ -13299,7 +13299,7 @@
         <v>0.24</v>
       </c>
       <c r="G31">
-        <v>0.47999999999999993</v>
+        <v>0.33599999999999997</v>
       </c>
       <c r="H31">
         <v>977.5</v>
@@ -13352,7 +13352,7 @@
         <v>0.3</v>
       </c>
       <c r="G32">
-        <v>0.48</v>
+        <v>0.33599999999999997</v>
       </c>
       <c r="H32">
         <v>977.5</v>
@@ -13405,7 +13405,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="G33">
-        <v>0.57599999999999996</v>
+        <v>0.40319999999999995</v>
       </c>
       <c r="H33">
         <v>850</v>
@@ -13458,7 +13458,7 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="G34">
-        <v>0.504</v>
+        <v>0.3528</v>
       </c>
       <c r="H34">
         <v>850</v>
@@ -13511,7 +13511,7 @@
         <v>0.45</v>
       </c>
       <c r="G35">
-        <v>0.55679999999999996</v>
+        <v>0.38975999999999994</v>
       </c>
       <c r="H35">
         <v>850</v>
@@ -13564,7 +13564,7 @@
         <v>0.16</v>
       </c>
       <c r="G36">
-        <v>0.48</v>
+        <v>0.33599999999999997</v>
       </c>
       <c r="H36">
         <v>977.5</v>
@@ -13617,7 +13617,7 @@
         <v>0.05</v>
       </c>
       <c r="G37">
-        <v>0.24480000000000002</v>
+        <v>0.17135999999999998</v>
       </c>
       <c r="H37">
         <v>918</v>
@@ -13670,7 +13670,7 @@
         <v>0.16700000000000001</v>
       </c>
       <c r="G38">
-        <v>0.25440000000000002</v>
+        <v>0.17807999999999999</v>
       </c>
       <c r="H38">
         <v>781.99999999999989</v>
@@ -13723,7 +13723,7 @@
         <v>0.05</v>
       </c>
       <c r="G39">
-        <v>0.24480000000000002</v>
+        <v>0.17135999999999998</v>
       </c>
       <c r="H39">
         <v>918</v>
@@ -13776,7 +13776,7 @@
         <v>0.05</v>
       </c>
       <c r="G40">
-        <v>0.24480000000000002</v>
+        <v>0.17135999999999998</v>
       </c>
       <c r="H40">
         <v>918</v>
@@ -13829,7 +13829,7 @@
         <v>0.05</v>
       </c>
       <c r="G41">
-        <v>0.28799999999999998</v>
+        <v>0.20159999999999997</v>
       </c>
       <c r="H41">
         <v>918</v>
@@ -13882,7 +13882,7 @@
         <v>0.05</v>
       </c>
       <c r="G42">
-        <v>0.28799999999999998</v>
+        <v>0.20159999999999997</v>
       </c>
       <c r="H42">
         <v>918</v>
@@ -13935,7 +13935,7 @@
         <v>0.05</v>
       </c>
       <c r="G43">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H43">
         <v>918</v>
@@ -13988,7 +13988,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
       <c r="G44">
-        <v>0.34079999999999999</v>
+        <v>0.23855999999999997</v>
       </c>
       <c r="H44">
         <v>1075.25</v>
@@ -14041,7 +14041,7 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="G45">
-        <v>0.34559999999999996</v>
+        <v>0.24192</v>
       </c>
       <c r="H45">
         <v>1075.25</v>
@@ -14094,7 +14094,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G46">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H46">
         <v>1173</v>
@@ -14147,7 +14147,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G47">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H47">
         <v>1173</v>
@@ -14200,7 +14200,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G48">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H48">
         <v>1173</v>
@@ -14253,7 +14253,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G49">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H49">
         <v>1173</v>
@@ -14306,7 +14306,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="G50">
-        <v>0.29759999999999998</v>
+        <v>0.20831999999999998</v>
       </c>
       <c r="H50">
         <v>1173</v>
@@ -16232,7 +16232,7 @@
         <v>95</v>
       </c>
       <c r="P86" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q86" t="s">
         <v>155</v>
@@ -16288,7 +16288,7 @@
         <v>95</v>
       </c>
       <c r="P87" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q87" t="s">
         <v>155</v>
@@ -16680,7 +16680,7 @@
         <v>105</v>
       </c>
       <c r="P94" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q94" t="s">
         <v>155</v>
@@ -16736,7 +16736,7 @@
         <v>105</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q95" t="s">
         <v>155</v>
@@ -16848,7 +16848,7 @@
         <v>109</v>
       </c>
       <c r="P97" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q97" t="s">
         <v>155</v>
@@ -16904,7 +16904,7 @@
         <v>109</v>
       </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q98" t="s">
         <v>155</v>
@@ -16960,7 +16960,7 @@
         <v>110</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q99" t="s">
         <v>155</v>
@@ -17016,7 +17016,7 @@
         <v>110</v>
       </c>
       <c r="P100" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q100" t="s">
         <v>155</v>
@@ -17072,7 +17072,7 @@
         <v>112</v>
       </c>
       <c r="P101" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q101" t="s">
         <v>155</v>
@@ -17128,7 +17128,7 @@
         <v>112</v>
       </c>
       <c r="P102" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q102" t="s">
         <v>155</v>
@@ -17184,7 +17184,7 @@
         <v>114</v>
       </c>
       <c r="P103" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q103" t="s">
         <v>155</v>
@@ -17240,7 +17240,7 @@
         <v>114</v>
       </c>
       <c r="P104" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q104" t="s">
         <v>155</v>
@@ -17576,7 +17576,7 @@
         <v>126</v>
       </c>
       <c r="P110" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q110" t="s">
         <v>155</v>
@@ -17632,7 +17632,7 @@
         <v>126</v>
       </c>
       <c r="P111" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q111" t="s">
         <v>155</v>
@@ -18080,7 +18080,7 @@
         <v>139</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="Q119" t="s">
         <v>155</v>
@@ -18136,7 +18136,7 @@
         <v>139</v>
       </c>
       <c r="P120" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
       <c r="Q120" t="s">
         <v>155</v>
@@ -20635,7 +20635,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F93A87C-2F41-4875-9A66-B2772C50D3FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEC99E9-D27E-4968-9DED-06309F1E9553}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
